--- a/app/exceltemplates/粗利率集計テンプレート.xlsx
+++ b/app/exceltemplates/粗利率集計テンプレート.xlsx
@@ -2,13 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seika\Desktop\cursor\projects\見積り管理\quotes_manager\app\exceltemplates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9A4178-DB62-496B-87B1-56760A4A2BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21584470-6E44-466E-93E0-EBE82C1A589E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{90879E6A-22C1-461E-986D-79ADD0FD67C7}"/>
   </bookViews>
@@ -600,5 +595,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>